--- a/artfynd/A 54675-2024 artfynd.xlsx
+++ b/artfynd/A 54675-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65234404</v>
       </c>
       <c r="B2" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369999.7695146592</v>
+        <v>370000</v>
       </c>
       <c r="R2" t="n">
-        <v>6363090.505140794</v>
+        <v>6363091</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -761,19 +756,9 @@
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
